--- a/yudao-module-reagent/src/main/resources/templates/reagent-shipment-print.xlsx
+++ b/yudao-module-reagent/src/main/resources/templates/reagent-shipment-print.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangdayou\Desktop\yudao\ruoyi-vue-pro\yudao-module-reagent\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEEED22-811A-4863-B966-8338D4DC7B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9924B854-4E6D-4FDC-A8DD-8954B5E1E069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="150" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="交接单" sheetId="1" r:id="rId1"/>
@@ -60,61 +60,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
-    <t>发货日期:</t>
-  </si>
-  <si>
-    <t>项目号:</t>
-  </si>
-  <si>
     <t>${projectNo}</t>
   </si>
   <si>
-    <t>运输温度:</t>
-  </si>
-  <si>
     <t>${transportTemp}</t>
   </si>
   <si>
-    <t>温度记录仪:</t>
-  </si>
-  <si>
-    <t>${hasTempLogger}</t>
-  </si>
-  <si>
-    <t>发货单位:</t>
-  </si>
-  <si>
     <t>${consignorUnit}</t>
   </si>
   <si>
-    <t>接收单位:</t>
-  </si>
-  <si>
     <t>${receiverUnit}</t>
   </si>
   <si>
-    <t>发货地址:</t>
-  </si>
-  <si>
-    <t>接收地址:</t>
-  </si>
-  <si>
-    <t>${receiverAddress}</t>
-  </si>
-  <si>
-    <t>发货人:</t>
-  </si>
-  <si>
-    <t>${consignorName}</t>
-  </si>
-  <si>
-    <t>联系方式:</t>
-  </si>
-  <si>
     <t>${consignorPhone}</t>
-  </si>
-  <si>
-    <t>接收人:</t>
   </si>
   <si>
     <t>${receiverName}</t>
@@ -294,8 +252,682 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Receiver Signature</t>
+    <t>${shipmentDate}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>□</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Yes) → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>详细说明（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Specify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>□</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>否</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (No)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>□</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>否</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (No) → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>详细说明（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Specify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">The following shall be filled in by the receiver </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>以下由收货方填写</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Reagent Details </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试剂信息</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reagent Name
+试剂名称</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BAS ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Manufacturer
+制造商</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Size/Concentration
+规格/浓度</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat#
+货号</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lot#
+批号</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Number
+发货数量</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Storage temp
+储存温度</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>${item.expirationDate}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expiration date
+过期日期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>此表为随货文件，签收后请将此回执的扫描件发送至邮箱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:  ${consignorEmail}</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note: This form is the document that comes with the goods. Please send the scanned copy of this receipt to the mailbox  ${consignorEmail}  after confirmation.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>□</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Yes)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>${consignorAddress}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>${consignorName}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>${receiverAddress}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Receiving Unit Address</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+接收地址</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Shipment Date
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发货日期</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Shipping Temp
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>运输温度</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Delivery Unit 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发货单位</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Delivery Unit Address</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发货地址</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Contact Information
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>联系方式</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Consignor</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发货人</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Study No.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>项目号</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Data Logger</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+温度记录仪</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Receiving Unit
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接收单位</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Receiver</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接收人</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>${hasTempLogger}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Receiver Signature  </t>
     </r>
     <r>
       <rPr>
@@ -305,8 +937,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">
-接收人签名</t>
+      <t>接收人签名</t>
     </r>
     <r>
       <rPr>
@@ -317,369 +948,6 @@
       </rPr>
       <t>:</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>${shipmentDate}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>□</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Yes) → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>详细说明（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Specify</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>□</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>否</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (No)</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>□</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>否</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (No) → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>详细说明（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Specify</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">The following shall be filled in by the receiver </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>以下由收货方填写</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Reagent Details </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>试剂信息</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reagent Name
-试剂名称</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BAS ID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Manufacturer
-制造商</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Size/Concentration
-规格/浓度</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cat#
-货号</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lot#
-批号</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Number
-发货数量</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Storage temp
-储存温度</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>${item.expirationDate}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Expiration date
-过期日期</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>注</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>此表为随货文件，签收后请将此回执的扫描件发送至邮箱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:  ${consignorEmail}</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Note: This form is the document that comes with the goods. Please send the scanned copy of this receipt to the mailbox  ${consignorEmail}  after confirmation.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>□</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Yes)</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>${consignorAddress}</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -687,7 +955,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -699,18 +967,22 @@
       <b/>
       <sz val="16"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -748,13 +1020,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
@@ -788,12 +1053,6 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -841,6 +1100,24 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -858,7 +1135,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -998,13 +1275,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1032,10 +1322,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1044,12 +1331,30 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1059,6 +1364,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1068,21 +1385,60 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1092,70 +1448,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1482,7 +1784,7 @@
     <col min="2" max="2" width="16.5" customWidth="1"/>
     <col min="3" max="3" width="14.125" customWidth="1"/>
     <col min="4" max="4" width="15.625" customWidth="1"/>
-    <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="5" max="5" width="18.875" customWidth="1"/>
     <col min="6" max="6" width="15.625" customWidth="1"/>
     <col min="7" max="7" width="13.375" customWidth="1"/>
     <col min="8" max="8" width="15.625" customWidth="1"/>
@@ -1490,381 +1792,375 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="28"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="29"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="31"/>
+    </row>
+    <row r="3" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="37"/>
+    </row>
+    <row r="4" spans="1:9" ht="29.25">
+      <c r="A4" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+    </row>
+    <row r="5" spans="1:9" ht="33">
+      <c r="A5" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+    </row>
+    <row r="6" spans="1:9" ht="29.25">
+      <c r="A6" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+    </row>
+    <row r="7" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+    </row>
+    <row r="8" spans="1:9" ht="29.25">
+      <c r="A8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+    </row>
+    <row r="9" spans="1:9" ht="20.25" customHeight="1">
+      <c r="A9" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+    </row>
+    <row r="10" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A10" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="37"/>
+    </row>
+    <row r="11" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A11" s="45"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="47"/>
+    </row>
+    <row r="12" spans="1:9" ht="33">
+      <c r="A12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="19"/>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="20"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="21"/>
-    </row>
-    <row r="3" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A3" s="37" t="s">
+      <c r="E12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="39"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75">
-      <c r="A4" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="F12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75">
-      <c r="A5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75">
-      <c r="A6" s="9" t="s">
+    </row>
+    <row r="13" spans="1:9" ht="34.5" customHeight="1">
+      <c r="A13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="9" t="s">
+      <c r="F13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="G13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75">
-      <c r="A7" s="9" t="s">
+      <c r="I13" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="44"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+    </row>
+    <row r="15" spans="1:9" ht="26.25" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="49"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75">
-      <c r="A8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75">
-      <c r="A9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A10" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="47"/>
-    </row>
-    <row r="11" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A11" s="48"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="50"/>
-    </row>
-    <row r="12" spans="1:9" ht="29.25" customHeight="1">
-      <c r="A12" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="I12" s="35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="25.5">
-      <c r="A13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-    </row>
-    <row r="15" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A15" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="28"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="50"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1">
-      <c r="A17" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
+      <c r="A17" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="42"/>
     </row>
     <row r="18" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A18" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="23"/>
+      <c r="A18" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="33"/>
+      <c r="C18" s="34"/>
       <c r="D18" s="8" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="11" t="s">
-        <v>42</v>
+      <c r="G18" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" ht="33">
-      <c r="A19" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23"/>
+      <c r="A19" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="33"/>
+      <c r="C19" s="34"/>
       <c r="D19" s="8" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="12" t="s">
-        <v>41</v>
+      <c r="G19" s="11" t="s">
+        <v>26</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="43"/>
+      <c r="A21" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="54"/>
+      <c r="C21" s="14"/>
       <c r="D21" s="4"/>
       <c r="E21" s="5"/>
-      <c r="F21" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="G21" s="34"/>
+      <c r="F21" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="24"/>
       <c r="H21" s="4"/>
       <c r="I21" s="5"/>
     </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="17"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="17"/>
+    <row r="22" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A22" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="22"/>
+    </row>
+    <row r="23" spans="1:9" ht="15" customHeight="1">
+      <c r="A23" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="A21:B21"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="B7:D7"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="A22:I22"/>
@@ -1880,19 +2176,11 @@
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="A10:I11"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="F9:I9"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="87" orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>